--- a/model/Outputs/11. Interest rate/40/Summary.xlsx
+++ b/model/Outputs/11. Interest rate/40/Summary.xlsx
@@ -1,37 +1,64 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mailaub-my.sharepoint.com/personal/mo10_aub_edu_lb/Documents/3-Research/Elsa/Model 1/Github/Model-1/model/Outputs/11. Interest rate/40/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="2" documentId="11_40A27530635AFD7DE0376FA53E6251319CC36AA6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F85678D5-B766-46A2-8DD0-57CF11DE68F2}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0.11" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="0.1" sheetId="3" r:id="rId1"/>
+    <sheet name="0.2" sheetId="4" r:id="rId2"/>
+    <sheet name="0.3" sheetId="5" r:id="rId3"/>
+    <sheet name="0.4" sheetId="2" r:id="rId4"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="4">
+  <si>
+    <t>Prices</t>
+  </si>
+  <si>
+    <t>Feed-in Tariffs</t>
+  </si>
+  <si>
+    <t>Base NPV</t>
+  </si>
+  <si>
+    <t>NPV</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -46,93 +73,43 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -420,250 +397,1000 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:P5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1">
-      <c r="B1" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="n">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="B1" s="1">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1">
         <v>1</v>
       </c>
-      <c r="D1" s="1" t="n">
+      <c r="D1" s="1">
         <v>2</v>
       </c>
-      <c r="E1" s="1" t="n">
+      <c r="E1" s="1">
         <v>3</v>
       </c>
-      <c r="F1" s="1" t="n">
+      <c r="F1" s="1">
         <v>4</v>
       </c>
-      <c r="G1" s="1" t="n">
+      <c r="G1" s="1">
         <v>5</v>
       </c>
-      <c r="H1" s="1" t="n">
+      <c r="H1" s="1">
         <v>6</v>
       </c>
-      <c r="I1" s="1" t="n">
+      <c r="I1" s="1">
         <v>7</v>
       </c>
-      <c r="J1" s="1" t="n">
+      <c r="J1" s="1">
         <v>8</v>
       </c>
-      <c r="K1" s="1" t="n">
+      <c r="K1" s="1">
         <v>9</v>
       </c>
-      <c r="L1" s="1" t="n">
+      <c r="L1" s="1">
         <v>10</v>
       </c>
-      <c r="M1" s="1" t="n">
+      <c r="M1" s="1">
         <v>11</v>
       </c>
-      <c r="N1" s="1" t="n">
+      <c r="N1" s="1">
         <v>12</v>
       </c>
-      <c r="O1" s="1" t="n">
+      <c r="O1" s="1">
         <v>13</v>
       </c>
-      <c r="P1" s="1" t="n">
+      <c r="P1" s="1">
         <v>14</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t>Prices</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2">
         <v>0.35</v>
       </c>
-      <c r="C2" t="n">
+      <c r="C2">
         <v>0.36</v>
       </c>
-      <c r="D2" t="n">
+      <c r="D2">
         <v>0.37</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2">
         <v>0.38</v>
       </c>
-      <c r="F2" t="n">
+      <c r="F2">
         <v>0.39</v>
       </c>
-      <c r="G2" t="n">
+      <c r="G2">
         <v>0.4</v>
       </c>
-      <c r="H2" t="n">
+      <c r="H2">
         <v>0.41</v>
       </c>
-      <c r="I2" t="n">
+      <c r="I2">
         <v>0.42</v>
       </c>
-      <c r="J2" t="n">
+      <c r="J2">
         <v>0.43</v>
       </c>
-      <c r="K2" t="n">
-        <v>0.4400000000000001</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0.4500000000000001</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0.4600000000000001</v>
-      </c>
-      <c r="N2" t="n">
-        <v>0.4700000000000001</v>
-      </c>
-      <c r="O2" t="n">
-        <v>0.4800000000000001</v>
-      </c>
-      <c r="P2" t="n">
+      <c r="K2">
+        <v>0.44000000000000011</v>
+      </c>
+      <c r="L2">
+        <v>0.45000000000000012</v>
+      </c>
+      <c r="M2">
+        <v>0.46000000000000008</v>
+      </c>
+      <c r="N2">
+        <v>0.47000000000000008</v>
+      </c>
+      <c r="O2">
+        <v>0.48000000000000009</v>
+      </c>
+      <c r="P2">
         <v>0.4900000000000001</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>Feed-in Tariffs</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>0.0625</v>
-      </c>
-      <c r="C3" t="n">
-        <v>0.09326171875</v>
-      </c>
-      <c r="D3" t="n">
-        <v>0.1085224151611328</v>
-      </c>
-      <c r="E3" t="n">
-        <v>0.1389245837926865</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0.1690892354818061</v>
-      </c>
-      <c r="G3" t="n">
-        <v>0.1990182258296045</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0.2287133959403107</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0.2894811976658819</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0.3184696258091172</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0.3759935379058498</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0.4892437398462919</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0.7086660061058987</v>
-      </c>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>Base NPV</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>3276370.810888279</v>
-      </c>
-      <c r="C4" t="n">
-        <v>3276370.810888279</v>
-      </c>
-      <c r="D4" t="n">
-        <v>3276370.810888279</v>
-      </c>
-      <c r="E4" t="n">
-        <v>3276370.810888279</v>
-      </c>
-      <c r="F4" t="n">
-        <v>3276370.810888279</v>
-      </c>
-      <c r="G4" t="n">
-        <v>3276370.810888279</v>
-      </c>
-      <c r="H4" t="n">
-        <v>3276370.810888279</v>
-      </c>
-      <c r="I4" t="n">
-        <v>3276370.810888279</v>
-      </c>
-      <c r="J4" t="n">
-        <v>3276370.810888279</v>
-      </c>
-      <c r="K4" t="n">
-        <v>3276370.810888279</v>
-      </c>
-      <c r="L4" t="n">
-        <v>3276370.810888279</v>
-      </c>
-      <c r="M4" t="n">
-        <v>3276370.810888279</v>
-      </c>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>NPV</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>3371365.763856722</v>
-      </c>
-      <c r="C5" t="n">
-        <v>3297381.224992601</v>
-      </c>
-      <c r="D5" t="n">
-        <v>3389231.735316333</v>
-      </c>
-      <c r="E5" t="n">
-        <v>3351013.319203741</v>
-      </c>
-      <c r="F5" t="n">
-        <v>3333992.824953103</v>
-      </c>
-      <c r="G5" t="n">
-        <v>3344657.715845525</v>
-      </c>
-      <c r="H5" t="n">
-        <v>3376489.253446863</v>
-      </c>
-      <c r="I5" t="n">
-        <v>3277223.44148294</v>
-      </c>
-      <c r="J5" t="n">
-        <v>3343218.142570848</v>
-      </c>
-      <c r="K5" t="n">
-        <v>3360530.530875956</v>
-      </c>
-      <c r="L5" t="n">
-        <v>3338873.058031257</v>
-      </c>
-      <c r="M5" t="n">
-        <v>3310835.585110424</v>
-      </c>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>6.640625E-2</v>
+      </c>
+      <c r="C3">
+        <v>8.945465087890625E-2</v>
+      </c>
+      <c r="D3">
+        <v>0.1123680025339127</v>
+      </c>
+      <c r="E3">
+        <v>0.14274012751411649</v>
+      </c>
+      <c r="F3">
+        <v>0.16534125957946341</v>
+      </c>
+      <c r="G3">
+        <v>0.20278909884138269</v>
+      </c>
+      <c r="H3">
+        <v>0.23987123654800979</v>
+      </c>
+      <c r="I3">
+        <v>0.27659124400359569</v>
+      </c>
+      <c r="J3">
+        <v>0.32386108172620631</v>
+      </c>
+      <c r="K3">
+        <v>0.39925064938611809</v>
+      </c>
+      <c r="L3">
+        <v>0.51177406659280189</v>
+      </c>
+      <c r="M3">
+        <v>0.70253642232600799</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A4" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4">
+        <v>3443385.6512425579</v>
+      </c>
+      <c r="C4">
+        <v>3443385.6512425579</v>
+      </c>
+      <c r="D4">
+        <v>3443385.6512425579</v>
+      </c>
+      <c r="E4">
+        <v>3443385.6512425579</v>
+      </c>
+      <c r="F4">
+        <v>3443385.6512425579</v>
+      </c>
+      <c r="G4">
+        <v>3443385.6512425579</v>
+      </c>
+      <c r="H4">
+        <v>3443385.6512425579</v>
+      </c>
+      <c r="I4">
+        <v>3443385.6512425579</v>
+      </c>
+      <c r="J4">
+        <v>3443385.6512425579</v>
+      </c>
+      <c r="K4">
+        <v>3443385.6512425579</v>
+      </c>
+      <c r="L4">
+        <v>3443385.6512425579</v>
+      </c>
+      <c r="M4">
+        <v>3443385.6512425579</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5">
+        <v>3476356.6263508121</v>
+      </c>
+      <c r="C5">
+        <v>3479405.5714877439</v>
+      </c>
+      <c r="D5">
+        <v>3491652.7492734152</v>
+      </c>
+      <c r="E5">
+        <v>3452462.7887185048</v>
+      </c>
+      <c r="F5">
+        <v>3495071.4534897869</v>
+      </c>
+      <c r="G5">
+        <v>3449183.2114385832</v>
+      </c>
+      <c r="H5">
+        <v>3450120.036252141</v>
+      </c>
+      <c r="I5">
+        <v>3470270.5246679601</v>
+      </c>
+      <c r="J5">
+        <v>3449701.095869747</v>
+      </c>
+      <c r="K5">
+        <v>3449181.9292935119</v>
+      </c>
+      <c r="L5">
+        <v>3447517.6975232391</v>
+      </c>
+      <c r="M5">
+        <v>3452319.551782609</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="A1:P5"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="B1" s="1">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2</v>
+      </c>
+      <c r="E1" s="1">
+        <v>3</v>
+      </c>
+      <c r="F1" s="1">
+        <v>4</v>
+      </c>
+      <c r="G1" s="1">
+        <v>5</v>
+      </c>
+      <c r="H1" s="1">
+        <v>6</v>
+      </c>
+      <c r="I1" s="1">
+        <v>7</v>
+      </c>
+      <c r="J1" s="1">
+        <v>8</v>
+      </c>
+      <c r="K1" s="1">
+        <v>9</v>
+      </c>
+      <c r="L1" s="1">
+        <v>10</v>
+      </c>
+      <c r="M1" s="1">
+        <v>11</v>
+      </c>
+      <c r="N1" s="1">
+        <v>12</v>
+      </c>
+      <c r="O1" s="1">
+        <v>13</v>
+      </c>
+      <c r="P1" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.35</v>
+      </c>
+      <c r="C2">
+        <v>0.36</v>
+      </c>
+      <c r="D2">
+        <v>0.37</v>
+      </c>
+      <c r="E2">
+        <v>0.38</v>
+      </c>
+      <c r="F2">
+        <v>0.39</v>
+      </c>
+      <c r="G2">
+        <v>0.4</v>
+      </c>
+      <c r="H2">
+        <v>0.41</v>
+      </c>
+      <c r="I2">
+        <v>0.42</v>
+      </c>
+      <c r="J2">
+        <v>0.43</v>
+      </c>
+      <c r="K2">
+        <v>0.44000000000000011</v>
+      </c>
+      <c r="L2">
+        <v>0.45000000000000012</v>
+      </c>
+      <c r="M2">
+        <v>0.46000000000000008</v>
+      </c>
+      <c r="N2">
+        <v>0.47000000000000008</v>
+      </c>
+      <c r="O2">
+        <v>0.48000000000000009</v>
+      </c>
+      <c r="P2">
+        <v>0.4900000000000001</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>0</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
+        <v>7.8125E-3</v>
+      </c>
+      <c r="G3">
+        <v>2.730560302734375E-2</v>
+      </c>
+      <c r="H3">
+        <v>4.6703524887561798E-2</v>
+      </c>
+      <c r="I3">
+        <v>7.9518974143866217E-2</v>
+      </c>
+      <c r="J3">
+        <v>0.1101477321583673</v>
+      </c>
+      <c r="K3">
+        <v>0.14243654492853711</v>
+      </c>
+      <c r="L3">
+        <v>0.17445733532707949</v>
+      </c>
+      <c r="M3">
+        <v>0.20621232814907151</v>
+      </c>
+      <c r="N3">
+        <v>0.23955616510869879</v>
+      </c>
+      <c r="O3">
+        <v>0.27627924943380922</v>
+      </c>
+      <c r="P3">
+        <v>0.31264370988855722</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A4" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4">
+        <v>3443385.6512425579</v>
+      </c>
+      <c r="C4">
+        <v>3443385.6512425579</v>
+      </c>
+      <c r="D4">
+        <v>3443385.6512425579</v>
+      </c>
+      <c r="E4">
+        <v>3443385.6512425579</v>
+      </c>
+      <c r="F4">
+        <v>3443385.6512425579</v>
+      </c>
+      <c r="G4">
+        <v>3443385.6512425579</v>
+      </c>
+      <c r="H4">
+        <v>3443385.6512425579</v>
+      </c>
+      <c r="I4">
+        <v>3443385.6512425579</v>
+      </c>
+      <c r="J4">
+        <v>3443385.6512425579</v>
+      </c>
+      <c r="K4">
+        <v>3443385.6512425579</v>
+      </c>
+      <c r="L4">
+        <v>3443385.6512425579</v>
+      </c>
+      <c r="M4">
+        <v>3443385.6512425579</v>
+      </c>
+      <c r="N4">
+        <v>3443385.6512425579</v>
+      </c>
+      <c r="O4">
+        <v>3443385.6512425579</v>
+      </c>
+      <c r="P4">
+        <v>3443385.6512425579</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5">
+        <v>3443385.6512425579</v>
+      </c>
+      <c r="C5">
+        <v>3443385.6512425579</v>
+      </c>
+      <c r="D5">
+        <v>3443385.6512425579</v>
+      </c>
+      <c r="E5">
+        <v>3443385.6512425579</v>
+      </c>
+      <c r="F5">
+        <v>3472483.7694439478</v>
+      </c>
+      <c r="G5">
+        <v>3468683.5277370792</v>
+      </c>
+      <c r="H5">
+        <v>3467914.0421818011</v>
+      </c>
+      <c r="I5">
+        <v>3445147.9169031242</v>
+      </c>
+      <c r="J5">
+        <v>3451042.254042442</v>
+      </c>
+      <c r="K5">
+        <v>3448642.6902906322</v>
+      </c>
+      <c r="L5">
+        <v>3449831.1462352318</v>
+      </c>
+      <c r="M5">
+        <v>3452687.050963019</v>
+      </c>
+      <c r="N5">
+        <v>3455736.783181184</v>
+      </c>
+      <c r="O5">
+        <v>3444532.7104749242</v>
+      </c>
+      <c r="P5">
+        <v>3449275.6568768569</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <dimension ref="A1:P5"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="B1" s="1">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2</v>
+      </c>
+      <c r="E1" s="1">
+        <v>3</v>
+      </c>
+      <c r="F1" s="1">
+        <v>4</v>
+      </c>
+      <c r="G1" s="1">
+        <v>5</v>
+      </c>
+      <c r="H1" s="1">
+        <v>6</v>
+      </c>
+      <c r="I1" s="1">
+        <v>7</v>
+      </c>
+      <c r="J1" s="1">
+        <v>8</v>
+      </c>
+      <c r="K1" s="1">
+        <v>9</v>
+      </c>
+      <c r="L1" s="1">
+        <v>10</v>
+      </c>
+      <c r="M1" s="1">
+        <v>11</v>
+      </c>
+      <c r="N1" s="1">
+        <v>12</v>
+      </c>
+      <c r="O1" s="1">
+        <v>13</v>
+      </c>
+      <c r="P1" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.35</v>
+      </c>
+      <c r="C2">
+        <v>0.36</v>
+      </c>
+      <c r="D2">
+        <v>0.37</v>
+      </c>
+      <c r="E2">
+        <v>0.38</v>
+      </c>
+      <c r="F2">
+        <v>0.39</v>
+      </c>
+      <c r="G2">
+        <v>0.4</v>
+      </c>
+      <c r="H2">
+        <v>0.41</v>
+      </c>
+      <c r="I2">
+        <v>0.42</v>
+      </c>
+      <c r="J2">
+        <v>0.43</v>
+      </c>
+      <c r="K2">
+        <v>0.44000000000000011</v>
+      </c>
+      <c r="L2">
+        <v>0.45000000000000012</v>
+      </c>
+      <c r="M2">
+        <v>0.46000000000000008</v>
+      </c>
+      <c r="N2">
+        <v>0.47000000000000008</v>
+      </c>
+      <c r="O2">
+        <v>0.48000000000000009</v>
+      </c>
+      <c r="P2">
+        <v>0.4900000000000001</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>0</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>0</v>
+      </c>
+      <c r="K3">
+        <v>0</v>
+      </c>
+      <c r="L3">
+        <v>0</v>
+      </c>
+      <c r="M3">
+        <v>7.8125E-3</v>
+      </c>
+      <c r="N3">
+        <v>3.12042236328125E-2</v>
+      </c>
+      <c r="O3">
+        <v>5.4458886384963989E-2</v>
+      </c>
+      <c r="P3">
+        <v>7.7577291347552091E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A4" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4">
+        <v>3443385.6512425579</v>
+      </c>
+      <c r="C4">
+        <v>3443385.6512425579</v>
+      </c>
+      <c r="D4">
+        <v>3443385.6512425579</v>
+      </c>
+      <c r="E4">
+        <v>3443385.6512425579</v>
+      </c>
+      <c r="F4">
+        <v>3443385.6512425579</v>
+      </c>
+      <c r="G4">
+        <v>3443385.6512425579</v>
+      </c>
+      <c r="H4">
+        <v>3443385.6512425579</v>
+      </c>
+      <c r="I4">
+        <v>3443385.6512425579</v>
+      </c>
+      <c r="J4">
+        <v>3443385.6512425579</v>
+      </c>
+      <c r="K4">
+        <v>3443385.6512425579</v>
+      </c>
+      <c r="L4">
+        <v>3443385.6512425579</v>
+      </c>
+      <c r="M4">
+        <v>3443385.6512425579</v>
+      </c>
+      <c r="N4">
+        <v>3443385.6512425579</v>
+      </c>
+      <c r="O4">
+        <v>3443385.6512425579</v>
+      </c>
+      <c r="P4">
+        <v>3443385.6512425579</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5">
+        <v>3443385.6512425579</v>
+      </c>
+      <c r="C5">
+        <v>3443385.6512425579</v>
+      </c>
+      <c r="D5">
+        <v>3443385.6512425579</v>
+      </c>
+      <c r="E5">
+        <v>3443385.6512425579</v>
+      </c>
+      <c r="F5">
+        <v>3443385.6512425579</v>
+      </c>
+      <c r="G5">
+        <v>3443385.6512425579</v>
+      </c>
+      <c r="H5">
+        <v>3443385.6512425579</v>
+      </c>
+      <c r="I5">
+        <v>3443385.6512425579</v>
+      </c>
+      <c r="J5">
+        <v>3443385.6512425579</v>
+      </c>
+      <c r="K5">
+        <v>3443385.6512425579</v>
+      </c>
+      <c r="L5">
+        <v>3443385.6512425579</v>
+      </c>
+      <c r="M5">
+        <v>3476989.8479826809</v>
+      </c>
+      <c r="N5">
+        <v>3450303.104307326</v>
+      </c>
+      <c r="O5">
+        <v>3458394.3668860048</v>
+      </c>
+      <c r="P5">
+        <v>3468198.3697913121</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:P5"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="B1" s="1">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2</v>
+      </c>
+      <c r="E1" s="1">
+        <v>3</v>
+      </c>
+      <c r="F1" s="1">
+        <v>4</v>
+      </c>
+      <c r="G1" s="1">
+        <v>5</v>
+      </c>
+      <c r="H1" s="1">
+        <v>6</v>
+      </c>
+      <c r="I1" s="1">
+        <v>7</v>
+      </c>
+      <c r="J1" s="1">
+        <v>8</v>
+      </c>
+      <c r="K1" s="1">
+        <v>9</v>
+      </c>
+      <c r="L1" s="1">
+        <v>10</v>
+      </c>
+      <c r="M1" s="1">
+        <v>11</v>
+      </c>
+      <c r="N1" s="1">
+        <v>12</v>
+      </c>
+      <c r="O1" s="1">
+        <v>13</v>
+      </c>
+      <c r="P1" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.35</v>
+      </c>
+      <c r="C2">
+        <v>0.36</v>
+      </c>
+      <c r="D2">
+        <v>0.37</v>
+      </c>
+      <c r="E2">
+        <v>0.38</v>
+      </c>
+      <c r="F2">
+        <v>0.39</v>
+      </c>
+      <c r="G2">
+        <v>0.4</v>
+      </c>
+      <c r="H2">
+        <v>0.41</v>
+      </c>
+      <c r="I2">
+        <v>0.42</v>
+      </c>
+      <c r="J2">
+        <v>0.43</v>
+      </c>
+      <c r="K2">
+        <v>0.44000000000000011</v>
+      </c>
+      <c r="L2">
+        <v>0.45000000000000012</v>
+      </c>
+      <c r="M2">
+        <v>0.46000000000000008</v>
+      </c>
+      <c r="N2">
+        <v>0.47000000000000008</v>
+      </c>
+      <c r="O2">
+        <v>0.48000000000000009</v>
+      </c>
+      <c r="P2">
+        <v>0.4900000000000001</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>0</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>0</v>
+      </c>
+      <c r="K3">
+        <v>0</v>
+      </c>
+      <c r="L3">
+        <v>0</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3">
+        <v>0</v>
+      </c>
+      <c r="O3">
+        <v>0</v>
+      </c>
+      <c r="P3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A4" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4">
+        <v>3443385.6512425579</v>
+      </c>
+      <c r="C4">
+        <v>3443385.6512425579</v>
+      </c>
+      <c r="D4">
+        <v>3443385.6512425579</v>
+      </c>
+      <c r="E4">
+        <v>3443385.6512425579</v>
+      </c>
+      <c r="F4">
+        <v>3443385.6512425579</v>
+      </c>
+      <c r="G4">
+        <v>3443385.6512425579</v>
+      </c>
+      <c r="H4">
+        <v>3443385.6512425579</v>
+      </c>
+      <c r="I4">
+        <v>3443385.6512425579</v>
+      </c>
+      <c r="J4">
+        <v>3443385.6512425579</v>
+      </c>
+      <c r="K4">
+        <v>3443385.6512425579</v>
+      </c>
+      <c r="L4">
+        <v>3443385.6512425579</v>
+      </c>
+      <c r="M4">
+        <v>3443385.6512425579</v>
+      </c>
+      <c r="N4">
+        <v>3443385.6512425579</v>
+      </c>
+      <c r="O4">
+        <v>3443385.6512425579</v>
+      </c>
+      <c r="P4">
+        <v>3443385.6512425579</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5">
+        <v>3443385.6512425579</v>
+      </c>
+      <c r="C5">
+        <v>3443385.6512425579</v>
+      </c>
+      <c r="D5">
+        <v>3443385.6512425579</v>
+      </c>
+      <c r="E5">
+        <v>3443385.6512425579</v>
+      </c>
+      <c r="F5">
+        <v>3443385.6512425579</v>
+      </c>
+      <c r="G5">
+        <v>3443385.6512425579</v>
+      </c>
+      <c r="H5">
+        <v>3443385.6512425579</v>
+      </c>
+      <c r="I5">
+        <v>3443385.6512425579</v>
+      </c>
+      <c r="J5">
+        <v>3443385.6512425579</v>
+      </c>
+      <c r="K5">
+        <v>3443385.6512425579</v>
+      </c>
+      <c r="L5">
+        <v>3443385.6512425579</v>
+      </c>
+      <c r="M5">
+        <v>3443385.6512425579</v>
+      </c>
+      <c r="N5">
+        <v>3443385.6512425579</v>
+      </c>
+      <c r="O5">
+        <v>3443385.6512425579</v>
+      </c>
+      <c r="P5">
+        <v>3443385.6512425579</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
